--- a/membership_forms/023_new_member_fitness_assessment_form--membership_forms.xlsx
+++ b/membership_forms/023_new_member_fitness_assessment_form--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'hypertension',_'value':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'hypertension', 'value': 'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes',_'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'diabetes', 'value': 'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'heart_disease',_'value':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'heart_disease', 'value': 'heart_disease'}</t>
+          <t>heart disease</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'high_cholesterol',_'value':_'high_cholesterol'}</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'high_cholesterol', 'value': 'high_cholesterol'}</t>
+          <t>high cholesterol</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'stroke',_'value':_'stroke'}</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'stroke', 'value': 'stroke'}</t>
+          <t>stroke</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'statins',_'value':_'statins'}</t>
+          <t>statins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'statins', 'value': 'statins'}</t>
+          <t>statins</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'beta_blockers',_'value':_'beta_blockers'}</t>
+          <t>beta_blockers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'beta_blockers', 'value': 'beta_blockers'}</t>
+          <t>beta blockers</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'diuretics',_'value':_'diuretics'}</t>
+          <t>diuretics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'diuretics', 'value': 'diuretics'}</t>
+          <t>diuretics</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'pain_relievers',_'value':_'pain_relievers'}</t>
+          <t>pain_relievers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'pain_relievers', 'value': 'pain_relievers'}</t>
+          <t>pain relievers</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'blood_pressure_meds',_'value':_'blood_pressure_meds'}</t>
+          <t>blood_pressure_meds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'blood_pressure_meds', 'value': 'blood_pressure_meds'}</t>
+          <t>blood pressure meds</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'blood_thinners',_'value':_'blood_thinners'}</t>
+          <t>blood_thinners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'blood_thinners', 'value': 'blood_thinners'}</t>
+          <t>blood thinners</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'insulin',_'value':_'insulin'}</t>
+          <t>insulin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'insulin', 'value': 'insulin'}</t>
+          <t>insulin</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'peanuts',_'value':_'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'peanuts', 'value': 'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish',_'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'shellfish', 'value': 'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'dairy',_'value':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'dairy', 'value': 'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'gluten',_'value':_'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'gluten', 'value': 'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish',_'value':_'shellfish'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'shellfish', 'value': 'shellfish'}</t>
+          <t>soy</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'soy',_'value':_'soy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'soy', 'value': 'soy'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>emergency_contact_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>mom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>mom</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'mom',_'value':_'mom'}</t>
+          <t>dad</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'mom', 'value': 'mom'}</t>
+          <t>dad</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'dad',_'value':_'dad'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'dad', 'value': 'dad'}</t>
+          <t>brother</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'brother',_'value':_'brother'}</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'brother', 'value': 'brother'}</t>
+          <t>sister</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'sister',_'value':_'sister'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'sister', 'value': 'sister'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'daily', 'value': 'daily'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'weekly', 'value': 'weekly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'monthly', 'value': 'monthly'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>exercise_frequency_choices</t>
+          <t>exercise_type_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'never', 'value': 'never'}</t>
+          <t>cardio</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'cardio',_'value':_'cardio'}</t>
+          <t>strength_training</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'cardio', 'value': 'cardio'}</t>
+          <t>strength training</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'strength_training',_'value':_'strength_training'}</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'strength_training', 'value': 'strength_training'}</t>
+          <t>flexibility</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'flexibility',_'value':_'flexibility'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'flexibility', 'value': 'flexibility'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>exercise_type_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
